--- a/Bin/A-QIP-WS009-01D.xlsx
+++ b/Bin/A-QIP-WS009-01D.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP SOURCE CODE QC 20251101\Bin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lys_erp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9241A5C-E111-46B8-9AB0-2E7C27E1B8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -419,7 +420,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="15">
     <font>
       <sz val="11"/>
@@ -700,56 +701,56 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,9 +770,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -809,9 +810,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -846,7 +847,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -881,7 +882,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1054,7 +1055,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1764,23 +1765,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="71.25" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
     </row>
     <row r="2" spans="1:15" ht="14.25" hidden="1" customHeight="1">
       <c r="A2" s="4"/>
@@ -1800,49 +1801,49 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="36.75" customHeight="1">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="19" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="20"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:15" ht="42" customHeight="1">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20"/>
     </row>
     <row r="5" spans="1:15" ht="57.75" customHeight="1">
-      <c r="A5" s="13"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
       <c r="F5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1865,117 +1866,119 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="26"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:15" ht="60.75" customHeight="1">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="10" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="26"/>
+      <c r="F7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="26"/>
+      <c r="H7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H8:I15"/>
+    <mergeCell ref="D7:E7"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:C15"/>
     <mergeCell ref="J1:O1"/>
@@ -1992,20 +1995,19 @@
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="F8:G15"/>
-    <mergeCell ref="H8:I15"/>
-    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0.1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
   <headerFooter>
-    <oddFooter xml:space="preserve">&amp;R&amp;"Arial,Regular"A-QIP-WS009-01D     </oddFooter>
+    <oddFooter xml:space="preserve">&amp;R&amp;"Arial,Regular"A-QIP-WS009-01D 
+QIP/VII/17/01     </oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
@@ -2014,7 +2016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
